--- a/public/モニタリングシート_様式A.xlsx
+++ b/public/モニタリングシート_様式A.xlsx
@@ -692,9 +692,9 @@
   <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
+    <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="1.5" customWidth="1"/>
-    <col min="4" max="15" width="12" customWidth="1"/>
+    <col min="4" max="15" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -803,7 +803,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
     </row>
-    <row r="7" ht="42" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="5"/>
@@ -828,7 +828,7 @@
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
     </row>
-    <row r="8" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>16</v>
       </c>
@@ -857,7 +857,7 @@
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
     </row>
-    <row r="9" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="14"/>
       <c r="C9" s="5"/>
@@ -882,7 +882,7 @@
       <c r="N9" s="16"/>
       <c r="O9" s="16"/>
     </row>
-    <row r="10" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="14"/>
       <c r="C10" s="5"/>
@@ -903,7 +903,7 @@
       <c r="N10" s="18"/>
       <c r="O10" s="18"/>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -932,7 +932,7 @@
       <c r="N11" s="21"/>
       <c r="O11" s="21"/>
     </row>
-    <row r="12" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="22"/>
       <c r="C12" s="23"/>
       <c r="D12" s="24" t="s">
@@ -956,7 +956,7 @@
       <c r="N12" s="25"/>
       <c r="O12" s="25"/>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="24"/>
@@ -972,7 +972,7 @@
       <c r="N13" s="25"/>
       <c r="O13" s="25"/>
     </row>
-    <row r="14" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="22"/>
       <c r="C14" s="23"/>
       <c r="D14" s="24"/>
@@ -988,7 +988,7 @@
       <c r="N14" s="25"/>
       <c r="O14" s="25"/>
     </row>
-    <row r="15" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="22"/>
       <c r="C15" s="23"/>
       <c r="D15" s="24"/>
@@ -1004,7 +1004,7 @@
       <c r="N15" s="25"/>
       <c r="O15" s="25"/>
     </row>
-    <row r="16" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="22"/>
       <c r="C16" s="23"/>
       <c r="D16" s="24"/>
@@ -1020,7 +1020,7 @@
       <c r="N16" s="25"/>
       <c r="O16" s="25"/>
     </row>
-    <row r="17" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="22"/>
       <c r="C17" s="23"/>
       <c r="D17" s="24"/>
@@ -1036,7 +1036,7 @@
       <c r="N17" s="25"/>
       <c r="O17" s="25"/>
     </row>
-    <row r="18" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
       <c r="B18" s="27"/>
       <c r="C18" s="28"/>
@@ -1122,6 +1122,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.4" header="0.3" footer="0.2"/>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>